--- a/stat4110-schedule.xlsx
+++ b/stat4110-schedule.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AliPe\Documents\GitHub Repositories\Ali-Raisolsadat.github.io\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74E47C69-9E59-48D3-A507-0D0AF6110BDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91B0D8D3-D2D7-4142-8DCB-75A454E1154D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9270" yWindow="675" windowWidth="16995" windowHeight="14805" xr2:uid="{E80023EF-6428-48D2-ABA1-FC32C6C952F1}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E80023EF-6428-48D2-ABA1-FC32C6C952F1}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="59">
   <si>
     <t>Week (Mon–Fri)</t>
   </si>
@@ -164,12 +164,6 @@
     <t>Homework Review Chapter 2</t>
   </si>
   <si>
-    <t>Homework Review Chapter 3</t>
-  </si>
-  <si>
-    <t>Homework Review Chapter 4</t>
-  </si>
-  <si>
     <t>Apr 13–17</t>
   </si>
   <si>
@@ -200,9 +194,6 @@
     <t xml:space="preserve">Quiz 4 </t>
   </si>
   <si>
-    <t>Assignment 2 Review</t>
-  </si>
-  <si>
     <t>Assignment 2 Due Mar 20</t>
   </si>
   <si>
@@ -210,6 +201,18 @@
   </si>
   <si>
     <t>Lecture 0 (Chapter 1)</t>
+  </si>
+  <si>
+    <t>Homework Review Chapter 4, 5</t>
+  </si>
+  <si>
+    <t>Final Assignment Review/QA</t>
+  </si>
+  <si>
+    <t>Final Assignment Published Mar 25</t>
+  </si>
+  <si>
+    <t>Homework Review Chapter 3 &amp; Assignment 2 Review</t>
   </si>
 </sst>
 </file>
@@ -253,7 +256,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -264,6 +267,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -606,8 +610,8 @@
   <cols>
     <col min="1" max="1" width="15.140625" bestFit="1" customWidth="1"/>
     <col min="2" max="3" width="38.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="27.42578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="49.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="29.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="51.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -624,7 +628,7 @@
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
@@ -632,7 +636,7 @@
         <v>4</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>20</v>
@@ -672,7 +676,7 @@
         <v>24</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>19</v>
@@ -692,7 +696,7 @@
         <v>25</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
@@ -703,10 +707,10 @@
         <v>26</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>19</v>
@@ -726,7 +730,7 @@
         <v>11</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
@@ -734,13 +738,13 @@
         <v>12</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>41</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>19</v>
@@ -751,16 +755,16 @@
         <v>13</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
@@ -768,33 +772,33 @@
         <v>14</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>54</v>
+        <v>37</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>15</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>38</v>
+        <v>28</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>50</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
@@ -802,30 +806,30 @@
         <v>16</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+        <v>28</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>17</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>30</v>
+        <v>43</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>55</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>19</v>
@@ -835,14 +839,14 @@
       <c r="A14" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="B14" s="2" t="s">
-        <v>31</v>
+      <c r="B14" s="3" t="s">
+        <v>51</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>43</v>
+        <v>56</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>19</v>
@@ -850,10 +854,10 @@
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>45</v>
+        <v>42</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>56</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>19</v>
@@ -862,7 +866,7 @@
         <v>19</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
@@ -873,6 +877,7 @@
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B17" s="3"/>
+      <c r="C17" s="4"/>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="2"/>
@@ -949,6 +954,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup scale="79" fitToHeight="0" orientation="landscape" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
+  <pageSetup scale="77" fitToHeight="0" orientation="landscape" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
 </worksheet>
 </file>
--- a/stat4110-schedule.xlsx
+++ b/stat4110-schedule.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AliPe\Documents\GitHub Repositories\Ali-Raisolsadat.github.io\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91B0D8D3-D2D7-4142-8DCB-75A454E1154D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B32A100B-3D0C-4ED4-9D51-915CA49DD008}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E80023EF-6428-48D2-ABA1-FC32C6C952F1}"/>
+    <workbookView xWindow="2730" yWindow="675" windowWidth="16995" windowHeight="14805" xr2:uid="{E80023EF-6428-48D2-ABA1-FC32C6C952F1}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="60">
   <si>
     <t>Week (Mon–Fri)</t>
   </si>
@@ -167,9 +167,6 @@
     <t>Apr 13–17</t>
   </si>
   <si>
-    <t>Lecture 3 (Chapter 5)</t>
-  </si>
-  <si>
     <t>Deliverables</t>
   </si>
   <si>
@@ -213,6 +210,12 @@
   </si>
   <si>
     <t>Homework Review Chapter 3 &amp; Assignment 2 Review</t>
+  </si>
+  <si>
+    <t>Holiday (Easter)</t>
+  </si>
+  <si>
+    <t>Holiday (Good Friday)</t>
   </si>
 </sst>
 </file>
@@ -256,7 +259,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -268,6 +271,9 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -628,7 +634,7 @@
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
@@ -636,7 +642,7 @@
         <v>4</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>20</v>
@@ -676,7 +682,7 @@
         <v>24</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>19</v>
@@ -696,7 +702,7 @@
         <v>25</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
@@ -730,7 +736,7 @@
         <v>11</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
@@ -744,7 +750,7 @@
         <v>41</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>19</v>
@@ -764,7 +770,7 @@
         <v>36</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
@@ -792,13 +798,13 @@
         <v>28</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
@@ -815,7 +821,7 @@
         <v>30</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -825,11 +831,11 @@
       <c r="B13" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="C13" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>55</v>
+      <c r="C13" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>59</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>19</v>
@@ -839,14 +845,14 @@
       <c r="A14" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="B14" s="3" t="s">
-        <v>51</v>
+      <c r="B14" s="5" t="s">
+        <v>58</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>19</v>
@@ -857,16 +863,16 @@
         <v>42</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>19</v>
+        <v>55</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>55</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
